--- a/LoanOfficer-A/2026/169 Thongam bala.xlsx
+++ b/LoanOfficer-A/2026/169 Thongam bala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>2800</v>
+        <v>11200</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>21000</v>
+        <v>12600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -926,9 +926,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>46115</v>
+      </c>
+      <c r="C5" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -952,9 +958,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>46125</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -978,9 +990,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>46131</v>
+      </c>
+      <c r="C7" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1004,9 +1022,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46143</v>
+      </c>
+      <c r="C8" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1030,9 +1054,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46150</v>
+      </c>
+      <c r="C9" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1056,9 +1086,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C10" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>

--- a/LoanOfficer-A/2026/169 Thongam bala.xlsx
+++ b/LoanOfficer-A/2026/169 Thongam bala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>11200</v>
+        <v>14000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>12600</v>
+        <v>9800</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1118,9 +1118,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>46164</v>
+      </c>
+      <c r="C11" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>
@@ -1144,9 +1150,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C12" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>

--- a/LoanOfficer-A/2026/169 Thongam bala.xlsx
+++ b/LoanOfficer-A/2026/169 Thongam bala.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>14000</v>
+        <v>15400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>9800</v>
+        <v>8400</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1182,9 +1182,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>46178</v>
+      </c>
+      <c r="C13" s="4">
+        <v>1400</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
